--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は896段落143表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は926段落145表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>896</v>
+        <v>926</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>36</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>896段落143表36図</t>
+          <t>926段落145表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新896段落（8段落の差）</t>
+          <t>受領888段落 対 最新926段落（38段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -890,7 +890,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>町別データシートの将来人口、見える化の画面の写しの点検ほか。**加筆はこの版に対して行われている。**</t>
+          <t>町別データシートの将来人口、見える化の画面の写しの点検ほか。加筆はこの版に対して行われている。</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は926段落145表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は928段落145表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>145</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>926段落145表36図</t>
+          <t>928段落145表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新926段落（38段落の差）</t>
+          <t>受領888段落 対 最新928段落（40段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は928段落145表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は928段落143表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -987,7 +987,7 @@
         <v>928</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>36</v>
@@ -1122,11 +1122,11 @@
           <t>6,436円</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="15" t="n">
-        <v>6</v>
+      <c r="C6" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
           <t>9,031,900,444</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="15" t="n">
-        <v>1</v>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
     <row r="21" ht="54" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>受領ファイルの数が当方より少ないものは、そのまま差し替えると失われます（8語）。
+          <t>受領ファイルの数が当方より少ないものは、そのまま差し替えると失われます（6語）。
 「R8実績」だけは受領ファイルの方が多く、これは是正前の記述が残っているためです。
 ※（案）の注記のうち「令和8年10月1日のデータないため1月1日を採用」とあるとおり、加筆の側でも時点の扱いを課題として認識されています。</t>
         </is>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>928段落145表36図</t>
+          <t>928段落143表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>対照した15語のうち8語が受領ファイルにない</t>
+          <t>対照した15語のうち6語が受領ファイルにない</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は928段落143表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は942段落145表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>928</v>
+        <v>942</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>36</v>
@@ -1360,7 +1360,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>928段落143表36図</t>
+          <t>942段落145表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新928段落（40段落の差）</t>
+          <t>受領888段落 対 最新942段落（54段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は942段落145表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は949段落146表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>36</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>942段落145表36図</t>
+          <t>949段落146表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新942段落（54段落の差）</t>
+          <t>受領888段落 対 最新949段落（61段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は949段落146表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は951段落146表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>146</v>
@@ -1360,7 +1360,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>949段落146表36図</t>
+          <t>951段落146表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新949段落（61段落の差）</t>
+          <t>受領888段落 対 最新951段落（63段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は951段落146表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は973段落148表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>951</v>
+        <v>973</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>36</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>951段落146表36図</t>
+          <t>973段落148表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新951段落（63段落の差）</t>
+          <t>受領888段落 対 最新973段落（85段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は973段落148表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1000段落151表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>973</v>
+        <v>1000</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>36</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>973段落148表36図</t>
+          <t>1000段落151表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新973段落（85段落の差）</t>
+          <t>受領888段落 対 最新1000段落（112段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1000段落151表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1001段落151表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>151</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1000段落151表36図</t>
+          <t>1001段落151表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新1000段落（112段落の差）</t>
+          <t>受領888段落 対 最新1001段落（113段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1001段落151表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1024段落152表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1001</v>
+        <v>1024</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>36</v>
@@ -1162,7 +1162,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1001段落151表36図</t>
+          <t>1024段落152表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新1001段落（113段落の差）</t>
+          <t>受領888段落 対 最新1024段落（136段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1024段落152表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1027段落153表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>36</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1024段落152表36図</t>
+          <t>1027段落153表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新1024段落（136段落の差）</t>
+          <t>受領888段落 対 最新1027段落（139段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1027段落153表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1030段落153表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>153</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1027段落153表36図</t>
+          <t>1030段落153表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新1027段落（139段落の差）</t>
+          <t>受領888段落 対 最新1030段落（142段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1030段落153表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1038段落153表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>153</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1030段落153表36図</t>
+          <t>1038段落153表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新1030段落（142段落の差）</t>
+          <t>受領888段落 対 最新1038段落（150段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1038段落153表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1060段落156表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1038</v>
+        <v>1060</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>36</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1038段落153表36図</t>
+          <t>1060段落156表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新1038段落（150段落の差）</t>
+          <t>受領888段落 対 最新1060段落（172段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1060段落156表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1059段落156表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>156</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1060段落156表36図</t>
+          <t>1059段落156表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新1060段落（172段落の差）</t>
+          <t>受領888段落 対 最新1059段落（171段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">

--- a/output/第10期計画_素案への加筆版の点検.xlsx
+++ b/output/第10期計画_素案への加筆版の点検.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1059段落156表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
+          <t>加筆は令和8年9月10日 の素案（806段落130表36図）に対して行われています。当方の最新は1062段落156表36図で、令和8年9月15日・16日の作業がこの版には入っていません。そのまま差し替えると7日分が消えます。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>156</v>
@@ -1360,7 +1360,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1059段落156表36図</t>
+          <t>1062段落156表36図</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受領888段落 対 最新1059段落（171段落の差）</t>
+          <t>受領888段落 対 最新1062段落（174段落の差）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
